--- a/00 Raw data/SDG/Publications_by_SDG_-_National_Taipei_University_of_Technology.xlsx
+++ b/00 Raw data/SDG/Publications_by_SDG_-_National_Taipei_University_of_Technology.xlsx
@@ -90,7 +90,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2018 to 2025</t>
+          <t>2017 to 2025</t>
         </is>
       </c>
     </row>
@@ -157,7 +157,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8 July 2026</t>
+          <t>5 August 2026</t>
         </is>
       </c>
     </row>
@@ -169,7 +169,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16 July 2026</t>
+          <t>13 August 2026</t>
         </is>
       </c>
     </row>
@@ -212,10 +212,10 @@
         <v>16.0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="D13" t="n">
-        <v>102.0</v>
+        <v>111.0</v>
       </c>
     </row>
     <row r="14">
@@ -225,13 +225,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="C14" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="D14" t="n">
-        <v>574.0</v>
+        <v>599.0</v>
       </c>
     </row>
     <row r="15">
@@ -241,13 +241,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>779.0</v>
+        <v>831.0</v>
       </c>
       <c r="C15" t="n">
         <v>1.25</v>
       </c>
       <c r="D15" t="n">
-        <v>14089.0</v>
+        <v>16231.0</v>
       </c>
     </row>
     <row r="16">
@@ -257,13 +257,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>180.0</v>
+        <v>188.0</v>
       </c>
       <c r="C16" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="D16" t="n">
-        <v>1962.0</v>
+        <v>2057.0</v>
       </c>
     </row>
     <row r="17">
@@ -276,10 +276,10 @@
         <v>24.0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="D17" t="n">
-        <v>201.0</v>
+        <v>202.0</v>
       </c>
     </row>
     <row r="18">
@@ -289,13 +289,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>369.0</v>
+        <v>390.0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="D18" t="n">
-        <v>7952.0</v>
+        <v>8709.0</v>
       </c>
     </row>
     <row r="19">
@@ -305,13 +305,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1300.0</v>
+        <v>1452.0</v>
       </c>
       <c r="C19" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="D19" t="n">
-        <v>24440.0</v>
+        <v>29119.0</v>
       </c>
     </row>
     <row r="20">
@@ -321,13 +321,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>173.0</v>
+        <v>181.0</v>
       </c>
       <c r="C20" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="D20" t="n">
-        <v>3393.0</v>
+        <v>3692.0</v>
       </c>
     </row>
     <row r="21">
@@ -337,13 +337,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1081.0</v>
+        <v>1146.0</v>
       </c>
       <c r="C21" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="D21" t="n">
-        <v>18429.0</v>
+        <v>20716.0</v>
       </c>
     </row>
     <row r="22">
@@ -353,13 +353,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
       <c r="C22" t="n">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
       <c r="D22" t="n">
-        <v>219.0</v>
+        <v>261.0</v>
       </c>
     </row>
     <row r="23">
@@ -369,13 +369,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>379.0</v>
+        <v>406.0</v>
       </c>
       <c r="C23" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="D23" t="n">
-        <v>5486.0</v>
+        <v>6294.0</v>
       </c>
     </row>
     <row r="24">
@@ -385,13 +385,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>349.0</v>
+        <v>369.0</v>
       </c>
       <c r="C24" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="D24" t="n">
-        <v>7968.0</v>
+        <v>9214.0</v>
       </c>
     </row>
     <row r="25">
@@ -401,13 +401,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>270.0</v>
+        <v>287.0</v>
       </c>
       <c r="C25" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="D25" t="n">
-        <v>6523.0</v>
+        <v>7230.0</v>
       </c>
     </row>
     <row r="26">
@@ -417,13 +417,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>66.0</v>
+        <v>70.0</v>
       </c>
       <c r="C26" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="D26" t="n">
-        <v>1432.0</v>
+        <v>1699.0</v>
       </c>
     </row>
     <row r="27">
@@ -436,10 +436,10 @@
         <v>62.0</v>
       </c>
       <c r="C27" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="D27" t="n">
-        <v>608.0</v>
+        <v>672.0</v>
       </c>
     </row>
     <row r="28">
@@ -449,13 +449,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>44.0</v>
+        <v>46.0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="D28" t="n">
-        <v>303.0</v>
+        <v>317.0</v>
       </c>
     </row>
     <row r="29">
@@ -465,13 +465,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3897.0</v>
+        <v>4194.0</v>
       </c>
       <c r="C29" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="D29" t="n">
-        <v>68363.0</v>
+        <v>78356.0</v>
       </c>
     </row>
     <row r="30">
